--- a/sheets/조재수대금교본/검수/어매.xlsx
+++ b/sheets/조재수대금교본/검수/어매.xlsx
@@ -2842,17 +2842,9 @@
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="24"/>
       <c r="N5" s="21"/>
       <c r="O5" s="24"/>
@@ -2874,11 +2866,7 @@
         </is>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -2903,11 +2891,7 @@
         </is>
       </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="22"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
@@ -2996,17 +2980,9 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21"/>
       <c r="I9" s="22"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J9" s="21"/>
       <c r="K9" s="22"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
@@ -3021,19 +2997,11 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -3169,11 +3137,7 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -3181,11 +3145,7 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/어매.xlsx
+++ b/sheets/조재수대금교본/검수/어매.xlsx
@@ -2704,28 +2704,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2824,7 +2824,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2851,7 +2851,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
       <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -2970,7 +2970,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -2993,7 +2993,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3219,6 +3219,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
 </worksheet>
 </file>